--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99270</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99377</v>
+        <v>99383</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99276</v>
+        <v>99278</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99383</v>
+        <v>99385</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99385</v>
+        <v>99386</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99386</v>
+        <v>99392</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99392</v>
+        <v>99396</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99398</v>
+        <v>99400</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99400</v>
+        <v>99413</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99413</v>
+        <v>99415</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99415</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99428</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99428</v>
+        <v>99429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99429</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99436</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99436</v>
+        <v>99442</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99442</v>
+        <v>99454</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99454</v>
+        <v>99455</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99455</v>
+        <v>99458</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99351</v>
+        <v>99352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99458</v>
+        <v>99459</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 37960-2024 artfynd.xlsx
+++ b/artfynd/A 37960-2024 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136951483</v>
       </c>
       <c r="B2" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>136955986</v>
       </c>
       <c r="B3" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>136955988</v>
       </c>
       <c r="B4" t="n">
-        <v>99352</v>
+        <v>99355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
         <v>136951482</v>
       </c>
       <c r="B5" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,7 +1107,7 @@
         <v>136955984</v>
       </c>
       <c r="B6" t="n">
-        <v>99459</v>
+        <v>99462</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
